--- a/assets/data/SET100_ปี68.xlsx
+++ b/assets/data/SET100_ปี68.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOCKER_COMPOSE\n8n\SET100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DOCKER_COMPOSE\n8n\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA175B4-1634-41D0-83C1-455C1013B33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D92424-8717-434D-84CA-B68596211549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="158">
   <si>
     <t>PTT</t>
   </si>
@@ -472,6 +472,48 @@
   </si>
   <si>
     <t>Industry</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>^GSPC</t>
+  </si>
+  <si>
+    <t>S&amp;P 500</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>MarketIndex</t>
+  </si>
+  <si>
+    <t>^IXIC</t>
+  </si>
+  <si>
+    <t>Dow Jones Industrial Average</t>
+  </si>
+  <si>
+    <t>^DJI</t>
+  </si>
+  <si>
+    <t>^RUT</t>
+  </si>
+  <si>
+    <t>Russell 2000</t>
+  </si>
+  <si>
+    <t>Nasdaq Composite</t>
+  </si>
+  <si>
+    <t>^SETHD</t>
+  </si>
+  <si>
+    <t>^SET50</t>
+  </si>
+  <si>
+    <t>^SET</t>
   </si>
 </sst>
 </file>
@@ -518,12 +560,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="จุลภาค" xfId="1" builtinId="3"/>
@@ -805,17 +855,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF88573-70C1-4B91-9DD2-89AFA20FDDDF}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.875" customWidth="1"/>
-    <col min="3" max="3" width="21.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>138</v>
       </c>
@@ -831,16 +880,11 @@
         <f>'SET100'!D1</f>
         <v>Industry</v>
       </c>
-      <c r="E1" t="str">
-        <f>'SET100'!O1</f>
-        <v>SET50</v>
-      </c>
-      <c r="F1" t="str">
-        <f>'SET100'!P1</f>
-        <v>SETHD</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <f>'SET100'!A2</f>
         <v>1</v>
@@ -857,16 +901,8 @@
         <f>'SET100'!D2</f>
         <v>อิเล็กทรอนิกส์</v>
       </c>
-      <c r="E2">
-        <f>'SET100'!O2</f>
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <f>'SET100'!P2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <f>'SET100'!A3</f>
         <v>2</v>
@@ -883,16 +919,8 @@
         <f>'SET100'!D3</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E3">
-        <f>'SET100'!O3</f>
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <f>'SET100'!P3</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <f>'SET100'!A4</f>
         <v>3</v>
@@ -909,16 +937,8 @@
         <f>'SET100'!D4</f>
         <v>ขนส่ง</v>
       </c>
-      <c r="E4">
-        <f>'SET100'!O4</f>
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <f>'SET100'!P4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <f>'SET100'!A5</f>
         <v>4</v>
@@ -935,16 +955,8 @@
         <f>'SET100'!D5</f>
         <v>ICT</v>
       </c>
-      <c r="E5">
-        <f>'SET100'!O5</f>
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <f>'SET100'!P5</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <f>'SET100'!A6</f>
         <v>5</v>
@@ -961,16 +973,8 @@
         <f>'SET100'!D6</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E6">
-        <f>'SET100'!O6</f>
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <f>'SET100'!P6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <f>'SET100'!A7</f>
         <v>6</v>
@@ -987,16 +991,8 @@
         <f>'SET100'!D7</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E7">
-        <f>'SET100'!O7</f>
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <f>'SET100'!P7</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <f>'SET100'!A8</f>
         <v>7</v>
@@ -1013,16 +1009,8 @@
         <f>'SET100'!D8</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E8">
-        <f>'SET100'!O8</f>
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <f>'SET100'!P8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <f>'SET100'!A9</f>
         <v>8</v>
@@ -1039,16 +1027,8 @@
         <f>'SET100'!D9</f>
         <v>การแพทย์</v>
       </c>
-      <c r="E9">
-        <f>'SET100'!O9</f>
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <f>'SET100'!P9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <f>'SET100'!A10</f>
         <v>9</v>
@@ -1065,16 +1045,8 @@
         <f>'SET100'!D10</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E10">
-        <f>'SET100'!O10</f>
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <f>'SET100'!P10</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <f>'SET100'!A11</f>
         <v>10</v>
@@ -1091,16 +1063,8 @@
         <f>'SET100'!D11</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E11">
-        <f>'SET100'!O11</f>
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <f>'SET100'!P11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <f>'SET100'!A12</f>
         <v>11</v>
@@ -1117,16 +1081,8 @@
         <f>'SET100'!D12</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E12">
-        <f>'SET100'!O12</f>
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <f>'SET100'!P12</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <f>'SET100'!A13</f>
         <v>12</v>
@@ -1143,16 +1099,8 @@
         <f>'SET100'!D13</f>
         <v>วัสดุก่อสร้าง</v>
       </c>
-      <c r="E13">
-        <f>'SET100'!O13</f>
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <f>'SET100'!P13</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <f>'SET100'!A14</f>
         <v>13</v>
@@ -1169,16 +1117,8 @@
         <f>'SET100'!D14</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E14">
-        <f>'SET100'!O14</f>
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <f>'SET100'!P14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <f>'SET100'!A15</f>
         <v>14</v>
@@ -1195,16 +1135,8 @@
         <f>'SET100'!D15</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E15">
-        <f>'SET100'!O15</f>
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <f>'SET100'!P15</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <f>'SET100'!A16</f>
         <v>15</v>
@@ -1221,16 +1153,8 @@
         <f>'SET100'!D16</f>
         <v>ICT</v>
       </c>
-      <c r="E16">
-        <f>'SET100'!O16</f>
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <f>'SET100'!P16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <f>'SET100'!A17</f>
         <v>16</v>
@@ -1247,16 +1171,8 @@
         <f>'SET100'!D17</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E17">
-        <f>'SET100'!O17</f>
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <f>'SET100'!P17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <f>'SET100'!A18</f>
         <v>17</v>
@@ -1273,16 +1189,8 @@
         <f>'SET100'!D18</f>
         <v>การแพทย์</v>
       </c>
-      <c r="E18">
-        <f>'SET100'!O18</f>
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <f>'SET100'!P18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <f>'SET100'!A19</f>
         <v>18</v>
@@ -1299,16 +1207,8 @@
         <f>'SET100'!D19</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E19">
-        <f>'SET100'!O19</f>
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <f>'SET100'!P19</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <f>'SET100'!A20</f>
         <v>19</v>
@@ -1325,16 +1225,8 @@
         <f>'SET100'!D20</f>
         <v>ปิโตรเคมี</v>
       </c>
-      <c r="E20">
-        <f>'SET100'!O20</f>
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <f>'SET100'!P20</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <f>'SET100'!A21</f>
         <v>20</v>
@@ -1351,16 +1243,8 @@
         <f>'SET100'!D21</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E21">
-        <f>'SET100'!O21</f>
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <f>'SET100'!P21</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <f>'SET100'!A22</f>
         <v>21</v>
@@ -1377,16 +1261,8 @@
         <f>'SET100'!D22</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E22">
-        <f>'SET100'!O22</f>
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <f>'SET100'!P22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <f>'SET100'!A23</f>
         <v>22</v>
@@ -1403,16 +1279,8 @@
         <f>'SET100'!D23</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E23">
-        <f>'SET100'!O23</f>
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <f>'SET100'!P23</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <f>'SET100'!A24</f>
         <v>23</v>
@@ -1429,16 +1297,8 @@
         <f>'SET100'!D24</f>
         <v>อาหาร</v>
       </c>
-      <c r="E24">
-        <f>'SET100'!O24</f>
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <f>'SET100'!P24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <f>'SET100'!A25</f>
         <v>24</v>
@@ -1455,16 +1315,8 @@
         <f>'SET100'!D25</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E25">
-        <f>'SET100'!O25</f>
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <f>'SET100'!P25</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <f>'SET100'!A26</f>
         <v>25</v>
@@ -1481,16 +1333,8 @@
         <f>'SET100'!D26</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E26">
-        <f>'SET100'!O26</f>
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <f>'SET100'!P26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <f>'SET100'!A27</f>
         <v>26</v>
@@ -1507,16 +1351,8 @@
         <f>'SET100'!D27</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E27">
-        <f>'SET100'!O27</f>
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <f>'SET100'!P27</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <f>'SET100'!A28</f>
         <v>27</v>
@@ -1533,16 +1369,8 @@
         <f>'SET100'!D28</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E28">
-        <f>'SET100'!O28</f>
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <f>'SET100'!P28</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <f>'SET100'!A29</f>
         <v>28</v>
@@ -1559,16 +1387,8 @@
         <f>'SET100'!D29</f>
         <v>บรรจุภัณฑ์</v>
       </c>
-      <c r="E29">
-        <f>'SET100'!O29</f>
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <f>'SET100'!P29</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <f>'SET100'!A30</f>
         <v>29</v>
@@ -1585,16 +1405,8 @@
         <f>'SET100'!D30</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E30">
-        <f>'SET100'!O30</f>
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <f>'SET100'!P30</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <f>'SET100'!A31</f>
         <v>30</v>
@@ -1611,16 +1423,8 @@
         <f>'SET100'!D31</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E31">
-        <f>'SET100'!O31</f>
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <f>'SET100'!P31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <f>'SET100'!A32</f>
         <v>31</v>
@@ -1637,16 +1441,8 @@
         <f>'SET100'!D32</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E32">
-        <f>'SET100'!O32</f>
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <f>'SET100'!P32</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <f>'SET100'!A33</f>
         <v>32</v>
@@ -1663,16 +1459,8 @@
         <f>'SET100'!D33</f>
         <v>อาหาร</v>
       </c>
-      <c r="E33">
-        <f>'SET100'!O33</f>
-        <v>1</v>
-      </c>
-      <c r="F33">
-        <f>'SET100'!P33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <f>'SET100'!A34</f>
         <v>33</v>
@@ -1689,16 +1477,8 @@
         <f>'SET100'!D34</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E34">
-        <f>'SET100'!O34</f>
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <f>'SET100'!P34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <f>'SET100'!A35</f>
         <v>34</v>
@@ -1715,16 +1495,8 @@
         <f>'SET100'!D35</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E35">
-        <f>'SET100'!O35</f>
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <f>'SET100'!P35</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <f>'SET100'!A36</f>
         <v>35</v>
@@ -1741,16 +1513,8 @@
         <f>'SET100'!D36</f>
         <v>อิเล็กฯ</v>
       </c>
-      <c r="E36">
-        <f>'SET100'!O36</f>
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <f>'SET100'!P36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <f>'SET100'!A37</f>
         <v>36</v>
@@ -1767,16 +1531,8 @@
         <f>'SET100'!D37</f>
         <v>อิเล็กฯ</v>
       </c>
-      <c r="E37">
-        <f>'SET100'!O37</f>
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <f>'SET100'!P37</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <f>'SET100'!A38</f>
         <v>37</v>
@@ -1793,16 +1549,8 @@
         <f>'SET100'!D38</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E38">
-        <f>'SET100'!O38</f>
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <f>'SET100'!P38</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39">
         <f>'SET100'!A39</f>
         <v>38</v>
@@ -1819,16 +1567,8 @@
         <f>'SET100'!D39</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E39">
-        <f>'SET100'!O39</f>
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <f>'SET100'!P39</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40">
         <f>'SET100'!A40</f>
         <v>39</v>
@@ -1845,16 +1585,8 @@
         <f>'SET100'!D40</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E40">
-        <f>'SET100'!O40</f>
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <f>'SET100'!P40</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41">
         <f>'SET100'!A41</f>
         <v>40</v>
@@ -1871,16 +1603,8 @@
         <f>'SET100'!D41</f>
         <v>อาหาร</v>
       </c>
-      <c r="E41">
-        <f>'SET100'!O41</f>
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <f>'SET100'!P41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42">
         <f>'SET100'!A42</f>
         <v>41</v>
@@ -1897,16 +1621,8 @@
         <f>'SET100'!D42</f>
         <v>อาหาร</v>
       </c>
-      <c r="E42">
-        <f>'SET100'!O42</f>
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <f>'SET100'!P42</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43">
         <f>'SET100'!A43</f>
         <v>42</v>
@@ -1923,16 +1639,8 @@
         <f>'SET100'!D43</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E43">
-        <f>'SET100'!O43</f>
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <f>'SET100'!P43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44">
         <f>'SET100'!A44</f>
         <v>43</v>
@@ -1949,16 +1657,8 @@
         <f>'SET100'!D44</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E44">
-        <f>'SET100'!O44</f>
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <f>'SET100'!P44</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45">
         <f>'SET100'!A45</f>
         <v>44</v>
@@ -1975,16 +1675,8 @@
         <f>'SET100'!D45</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E45">
-        <f>'SET100'!O45</f>
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <f>'SET100'!P45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46">
         <f>'SET100'!A46</f>
         <v>45</v>
@@ -2001,16 +1693,8 @@
         <f>'SET100'!D46</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E46">
-        <f>'SET100'!O46</f>
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <f>'SET100'!P46</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47">
         <f>'SET100'!A47</f>
         <v>46</v>
@@ -2027,16 +1711,8 @@
         <f>'SET100'!D47</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E47">
-        <f>'SET100'!O47</f>
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <f>'SET100'!P47</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48">
         <f>'SET100'!A48</f>
         <v>47</v>
@@ -2053,16 +1729,8 @@
         <f>'SET100'!D48</f>
         <v>ธนาคาร</v>
       </c>
-      <c r="E48">
-        <f>'SET100'!O48</f>
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <f>'SET100'!P48</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <f>'SET100'!A49</f>
         <v>48</v>
@@ -2079,16 +1747,8 @@
         <f>'SET100'!D49</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E49">
-        <f>'SET100'!O49</f>
-        <v>1</v>
-      </c>
-      <c r="F49">
-        <f>'SET100'!P49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <f>'SET100'!A50</f>
         <v>49</v>
@@ -2105,16 +1765,8 @@
         <f>'SET100'!D50</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E50">
-        <f>'SET100'!O50</f>
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <f>'SET100'!P50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <f>'SET100'!A51</f>
         <v>50</v>
@@ -2131,16 +1783,8 @@
         <f>'SET100'!D51</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E51">
-        <f>'SET100'!O51</f>
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <f>'SET100'!P51</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <f>'SET100'!A52</f>
         <v>51</v>
@@ -2157,16 +1801,8 @@
         <f>'SET100'!D52</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E52">
-        <f>'SET100'!O52</f>
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <f>'SET100'!P52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <f>'SET100'!A53</f>
         <v>52</v>
@@ -2183,16 +1819,8 @@
         <f>'SET100'!D53</f>
         <v>อาหาร</v>
       </c>
-      <c r="E53">
-        <f>'SET100'!O53</f>
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <f>'SET100'!P53</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <f>'SET100'!A54</f>
         <v>53</v>
@@ -2209,16 +1837,8 @@
         <f>'SET100'!D54</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E54">
-        <f>'SET100'!O54</f>
-        <v>1</v>
-      </c>
-      <c r="F54">
-        <f>'SET100'!P54</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <f>'SET100'!A55</f>
         <v>54</v>
@@ -2235,16 +1855,8 @@
         <f>'SET100'!D55</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E55">
-        <f>'SET100'!O55</f>
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <f>'SET100'!P55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <f>'SET100'!A56</f>
         <v>55</v>
@@ -2261,16 +1873,8 @@
         <f>'SET100'!D56</f>
         <v>อาหาร</v>
       </c>
-      <c r="E56">
-        <f>'SET100'!O56</f>
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <f>'SET100'!P56</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <f>'SET100'!A57</f>
         <v>56</v>
@@ -2287,16 +1891,8 @@
         <f>'SET100'!D57</f>
         <v>การแพทย์</v>
       </c>
-      <c r="E57">
-        <f>'SET100'!O57</f>
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <f>'SET100'!P57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <f>'SET100'!A58</f>
         <v>57</v>
@@ -2313,16 +1909,8 @@
         <f>'SET100'!D58</f>
         <v>การแพทย์</v>
       </c>
-      <c r="E58">
-        <f>'SET100'!O58</f>
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <f>'SET100'!P58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <f>'SET100'!A59</f>
         <v>58</v>
@@ -2339,16 +1927,8 @@
         <f>'SET100'!D59</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E59">
-        <f>'SET100'!O59</f>
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <f>'SET100'!P59</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <f>'SET100'!A60</f>
         <v>59</v>
@@ -2365,16 +1945,8 @@
         <f>'SET100'!D60</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E60">
-        <f>'SET100'!O60</f>
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <f>'SET100'!P60</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <f>'SET100'!A61</f>
         <v>60</v>
@@ -2391,16 +1963,8 @@
         <f>'SET100'!D61</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E61">
-        <f>'SET100'!O61</f>
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <f>'SET100'!P61</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62">
         <f>'SET100'!A62</f>
         <v>61</v>
@@ -2417,16 +1981,8 @@
         <f>'SET100'!D62</f>
         <v>เกษตร</v>
       </c>
-      <c r="E62">
-        <f>'SET100'!O62</f>
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <f>'SET100'!P62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63">
         <f>'SET100'!A63</f>
         <v>62</v>
@@ -2443,16 +1999,8 @@
         <f>'SET100'!D63</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E63">
-        <f>'SET100'!O63</f>
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <f>'SET100'!P63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
         <f>'SET100'!A64</f>
         <v>63</v>
@@ -2469,16 +2017,8 @@
         <f>'SET100'!D64</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E64">
-        <f>'SET100'!O64</f>
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <f>'SET100'!P64</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
         <f>'SET100'!A65</f>
         <v>64</v>
@@ -2495,16 +2035,8 @@
         <f>'SET100'!D65</f>
         <v>ขนส่ง</v>
       </c>
-      <c r="E65">
-        <f>'SET100'!O65</f>
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <f>'SET100'!P65</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66">
         <f>'SET100'!A66</f>
         <v>65</v>
@@ -2521,16 +2053,8 @@
         <f>'SET100'!D66</f>
         <v>ขนส่ง</v>
       </c>
-      <c r="E66">
-        <f>'SET100'!O66</f>
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <f>'SET100'!P66</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
         <f>'SET100'!A67</f>
         <v>66</v>
@@ -2547,16 +2071,8 @@
         <f>'SET100'!D67</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E67">
-        <f>'SET100'!O67</f>
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <f>'SET100'!P67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
         <f>'SET100'!A68</f>
         <v>67</v>
@@ -2573,16 +2089,8 @@
         <f>'SET100'!D68</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E68">
-        <f>'SET100'!O68</f>
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <f>'SET100'!P68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
         <f>'SET100'!A69</f>
         <v>68</v>
@@ -2599,16 +2107,8 @@
         <f>'SET100'!D69</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E69">
-        <f>'SET100'!O69</f>
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <f>'SET100'!P69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70">
         <f>'SET100'!A70</f>
         <v>69</v>
@@ -2625,16 +2125,8 @@
         <f>'SET100'!D70</f>
         <v>พลังงาน</v>
       </c>
-      <c r="E70">
-        <f>'SET100'!O70</f>
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <f>'SET100'!P70</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71">
         <f>'SET100'!A71</f>
         <v>70</v>
@@ -2651,16 +2143,8 @@
         <f>'SET100'!D71</f>
         <v>อสังหาฯ</v>
       </c>
-      <c r="E71">
-        <f>'SET100'!O71</f>
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <f>'SET100'!P71</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72">
         <f>'SET100'!A72</f>
         <v>71</v>
@@ -2677,16 +2161,8 @@
         <f>'SET100'!D72</f>
         <v>การแพทย์</v>
       </c>
-      <c r="E72">
-        <f>'SET100'!O72</f>
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <f>'SET100'!P72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73">
         <f>'SET100'!A73</f>
         <v>72</v>
@@ -2703,16 +2179,8 @@
         <f>'SET100'!D73</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E73">
-        <f>'SET100'!O73</f>
-        <v>0</v>
-      </c>
-      <c r="F73">
-        <f>'SET100'!P73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74">
         <f>'SET100'!A74</f>
         <v>73</v>
@@ -2729,16 +2197,8 @@
         <f>'SET100'!D74</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E74">
-        <f>'SET100'!O74</f>
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <f>'SET100'!P74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75">
         <f>'SET100'!A75</f>
         <v>74</v>
@@ -2755,16 +2215,8 @@
         <f>'SET100'!D75</f>
         <v>ประกัน</v>
       </c>
-      <c r="E75">
-        <f>'SET100'!O75</f>
-        <v>0</v>
-      </c>
-      <c r="F75">
-        <f>'SET100'!P75</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76">
         <f>'SET100'!A76</f>
         <v>75</v>
@@ -2781,16 +2233,8 @@
         <f>'SET100'!D76</f>
         <v>ประกัน</v>
       </c>
-      <c r="E76">
-        <f>'SET100'!O76</f>
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <f>'SET100'!P76</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77">
         <f>'SET100'!A77</f>
         <v>76</v>
@@ -2807,16 +2251,8 @@
         <f>'SET100'!D77</f>
         <v>เกษตร</v>
       </c>
-      <c r="E77">
-        <f>'SET100'!O77</f>
-        <v>0</v>
-      </c>
-      <c r="F77">
-        <f>'SET100'!P77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78">
         <f>'SET100'!A78</f>
         <v>77</v>
@@ -2833,16 +2269,8 @@
         <f>'SET100'!D78</f>
         <v>ขนส่ง</v>
       </c>
-      <c r="E78">
-        <f>'SET100'!O78</f>
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <f>'SET100'!P78</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79">
         <f>'SET100'!A79</f>
         <v>80</v>
@@ -2859,16 +2287,8 @@
         <f>'SET100'!D79</f>
         <v>วัสดุฯ</v>
       </c>
-      <c r="E79">
-        <f>'SET100'!O79</f>
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <f>'SET100'!P79</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80">
         <f>'SET100'!A80</f>
         <v>79</v>
@@ -2885,16 +2305,8 @@
         <f>'SET100'!D80</f>
         <v>อาหาร</v>
       </c>
-      <c r="E80">
-        <f>'SET100'!O80</f>
-        <v>0</v>
-      </c>
-      <c r="F80">
-        <f>'SET100'!P80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81">
         <f>'SET100'!A81</f>
         <v>80</v>
@@ -2911,16 +2323,8 @@
         <f>'SET100'!D81</f>
         <v>อาหาร</v>
       </c>
-      <c r="E81">
-        <f>'SET100'!O81</f>
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <f>'SET100'!P81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82">
         <f>'SET100'!A82</f>
         <v>81</v>
@@ -2937,16 +2341,8 @@
         <f>'SET100'!D82</f>
         <v>เกษตร</v>
       </c>
-      <c r="E82">
-        <f>'SET100'!O82</f>
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <f>'SET100'!P82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83">
         <f>'SET100'!A83</f>
         <v>82</v>
@@ -2963,16 +2359,8 @@
         <f>'SET100'!D83</f>
         <v>พาณิชย์</v>
       </c>
-      <c r="E83">
-        <f>'SET100'!O83</f>
-        <v>0</v>
-      </c>
-      <c r="F83">
-        <f>'SET100'!P83</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84">
         <f>'SET100'!A84</f>
         <v>83</v>
@@ -2989,16 +2377,8 @@
         <f>'SET100'!D84</f>
         <v>ท่องเที่ยว</v>
       </c>
-      <c r="E84">
-        <f>'SET100'!O84</f>
-        <v>0</v>
-      </c>
-      <c r="F84">
-        <f>'SET100'!P84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85">
         <f>'SET100'!A85</f>
         <v>84</v>
@@ -3015,16 +2395,8 @@
         <f>'SET100'!D85</f>
         <v>ท่องเที่ยว</v>
       </c>
-      <c r="E85">
-        <f>'SET100'!O85</f>
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <f>'SET100'!P85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86">
         <f>'SET100'!A86</f>
         <v>85</v>
@@ -3041,16 +2413,8 @@
         <f>'SET100'!D86</f>
         <v>ขนส่ง</v>
       </c>
-      <c r="E86">
-        <f>'SET100'!O86</f>
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <f>'SET100'!P86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87">
         <f>'SET100'!A87</f>
         <v>86</v>
@@ -3067,16 +2431,8 @@
         <f>'SET100'!D87</f>
         <v>ขนส่ง</v>
       </c>
-      <c r="E87">
-        <f>'SET100'!O87</f>
-        <v>0</v>
-      </c>
-      <c r="F87">
-        <f>'SET100'!P87</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88">
         <f>'SET100'!A88</f>
         <v>87</v>
@@ -3093,16 +2449,8 @@
         <f>'SET100'!D88</f>
         <v>รับเหมา</v>
       </c>
-      <c r="E88">
-        <f>'SET100'!O88</f>
-        <v>0</v>
-      </c>
-      <c r="F88">
-        <f>'SET100'!P88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89">
         <f>'SET100'!A89</f>
         <v>88</v>
@@ -3119,16 +2467,8 @@
         <f>'SET100'!D89</f>
         <v>เทคโนโลยี</v>
       </c>
-      <c r="E89">
-        <f>'SET100'!O89</f>
-        <v>0</v>
-      </c>
-      <c r="F89">
-        <f>'SET100'!P89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90">
         <f>'SET100'!A90</f>
         <v>89</v>
@@ -3145,16 +2485,8 @@
         <f>'SET100'!D90</f>
         <v>เงินทุน</v>
       </c>
-      <c r="E90">
-        <f>'SET100'!O90</f>
-        <v>0</v>
-      </c>
-      <c r="F90">
-        <f>'SET100'!P90</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91">
         <f>'SET100'!A91</f>
         <v>90</v>
@@ -3171,16 +2503,8 @@
         <f>'SET100'!D91</f>
         <v>อาหาร</v>
       </c>
-      <c r="E91">
-        <f>'SET100'!O91</f>
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <f>'SET100'!P91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92">
         <f>'SET100'!A92</f>
         <v>91</v>
@@ -3197,16 +2521,8 @@
         <f>'SET100'!D92</f>
         <v>บริการ</v>
       </c>
-      <c r="E92">
-        <f>'SET100'!O92</f>
-        <v>0</v>
-      </c>
-      <c r="F92">
-        <f>'SET100'!P92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93">
         <f>'SET100'!A93</f>
         <v>92</v>
@@ -3223,16 +2539,8 @@
         <f>'SET100'!D93</f>
         <v>บริการ</v>
       </c>
-      <c r="E93">
-        <f>'SET100'!O93</f>
-        <v>0</v>
-      </c>
-      <c r="F93">
-        <f>'SET100'!P93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94">
         <f>'SET100'!A94</f>
         <v>93</v>
@@ -3249,16 +2557,8 @@
         <f>'SET100'!D94</f>
         <v>เทคโนโลยี</v>
       </c>
-      <c r="E94">
-        <f>'SET100'!O94</f>
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <f>'SET100'!P94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95">
         <f>'SET100'!A95</f>
         <v>94</v>
@@ -3275,16 +2575,8 @@
         <f>'SET100'!D95</f>
         <v>อุปโภคบริโภค</v>
       </c>
-      <c r="E95">
-        <f>'SET100'!O95</f>
-        <v>0</v>
-      </c>
-      <c r="F95">
-        <f>'SET100'!P95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96">
         <f>'SET100'!A96</f>
         <v>95</v>
@@ -3301,16 +2593,8 @@
         <f>'SET100'!D96</f>
         <v>อาหาร</v>
       </c>
-      <c r="E96">
-        <f>'SET100'!O96</f>
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <f>'SET100'!P96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <f>'SET100'!A97</f>
         <v>96</v>
@@ -3327,16 +2611,8 @@
         <f>'SET100'!D97</f>
         <v>อาหาร</v>
       </c>
-      <c r="E97">
-        <f>'SET100'!O97</f>
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <f>'SET100'!P97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <f>'SET100'!A98</f>
         <v>97</v>
@@ -3353,16 +2629,8 @@
         <f>'SET100'!D98</f>
         <v>แฟชั่น</v>
       </c>
-      <c r="E98">
-        <f>'SET100'!O98</f>
-        <v>0</v>
-      </c>
-      <c r="F98">
-        <f>'SET100'!P98</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <f>'SET100'!A99</f>
         <v>98</v>
@@ -3379,16 +2647,8 @@
         <f>'SET100'!D99</f>
         <v>อาหาร</v>
       </c>
-      <c r="E99">
-        <f>'SET100'!O99</f>
-        <v>0</v>
-      </c>
-      <c r="F99">
-        <f>'SET100'!P99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <f>'SET100'!A100</f>
         <v>99</v>
@@ -3405,16 +2665,8 @@
         <f>'SET100'!D100</f>
         <v>บริการ</v>
       </c>
-      <c r="E100">
-        <f>'SET100'!O100</f>
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <f>'SET100'!P100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <f>'SET100'!A101</f>
         <v>100</v>
@@ -3431,13 +2683,115 @@
         <f>'SET100'!D101</f>
         <v>บริการ</v>
       </c>
-      <c r="E101">
-        <f>'SET100'!O101</f>
-        <v>0</v>
-      </c>
-      <c r="F101">
-        <f>'SET100'!P101</f>
-        <v>0</v>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>9001</v>
+      </c>
+      <c r="B102" t="s">
+        <v>157</v>
+      </c>
+      <c r="D102" t="s">
+        <v>144</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>9002</v>
+      </c>
+      <c r="B103" t="s">
+        <v>156</v>
+      </c>
+      <c r="D103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>9003</v>
+      </c>
+      <c r="B104" t="s">
+        <v>155</v>
+      </c>
+      <c r="D104" t="s">
+        <v>144</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>9101</v>
+      </c>
+      <c r="B105" t="s">
+        <v>145</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" t="s">
+        <v>147</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>9102</v>
+      </c>
+      <c r="B106" t="s">
+        <v>149</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D106" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>9103</v>
+      </c>
+      <c r="B107" t="s">
+        <v>151</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D107" t="s">
+        <v>147</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>9104</v>
+      </c>
+      <c r="B108" t="s">
+        <v>152</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D108" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
